--- a/data/trans_orig/IQ28_P-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición</t>
+          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,75; 36,41</t>
+          <t>30,73; 36,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,15; 34,56</t>
+          <t>28,02; 34,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,13; 41,18</t>
+          <t>34,23; 41,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,54; 39,56</t>
+          <t>32,5; 39,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 33,91</t>
+          <t>28,39; 34,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,61; 46,61</t>
+          <t>37,67; 46,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,35; 36,95</t>
+          <t>32,43; 37,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,04; 33,38</t>
+          <t>29,13; 33,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,13; 43,08</t>
+          <t>37,28; 42,99</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,08; 33,58</t>
+          <t>28,12; 33,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 35,18</t>
+          <t>30,2; 35,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,45; 40,62</t>
+          <t>33,36; 40,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 36,97</t>
+          <t>30,79; 36,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,95; 35,1</t>
+          <t>30,13; 34,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,79; 41,23</t>
+          <t>33,88; 41,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 34,03</t>
+          <t>30,3; 34,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 34,37</t>
+          <t>30,76; 34,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,6; 39,8</t>
+          <t>34,53; 40,06</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,53; 37,41</t>
+          <t>31,32; 37,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,47; 35,75</t>
+          <t>29,66; 36,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,03; 37,09</t>
+          <t>27,12; 37,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,01; 37,19</t>
+          <t>31,18; 37,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,38</t>
+          <t>33,58; 40,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,29; 47,81</t>
+          <t>34,01; 46,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,16; 36,7</t>
+          <t>31,76; 36,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,46; 37,23</t>
+          <t>32,64; 37,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,72; 42,31</t>
+          <t>32,51; 41,91</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 35,72</t>
+          <t>31,76; 35,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,08; 36,8</t>
+          <t>33,2; 37,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,42; 52,02</t>
+          <t>34,58; 52,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,86; 36,76</t>
+          <t>32,77; 36,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,24; 37,98</t>
+          <t>33,14; 37,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,53; 45,15</t>
+          <t>35,5; 45,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,86; 35,62</t>
+          <t>32,73; 35,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,66; 36,61</t>
+          <t>33,68; 36,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,53; 49,13</t>
+          <t>36,35; 47,97</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,19; 37,64</t>
+          <t>33,03; 37,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,61; 37,3</t>
+          <t>32,72; 37,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,3; 44,22</t>
+          <t>35,7; 44,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,25; 39,58</t>
+          <t>34,37; 39,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,75; 39,12</t>
+          <t>33,53; 38,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,12; 45,31</t>
+          <t>37,06; 45,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,46; 37,97</t>
+          <t>34,44; 38,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,79; 37,09</t>
+          <t>33,82; 37,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37,73; 43,81</t>
+          <t>37,58; 43,87</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,06; 43,67</t>
+          <t>33,78; 44,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,09; 42,05</t>
+          <t>33,71; 42,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,85; 45,84</t>
+          <t>33,08; 46,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,43; 42,49</t>
+          <t>35,01; 42,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,7</t>
+          <t>34,58; 41,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,76; 51,89</t>
+          <t>38,97; 52,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,74; 41,84</t>
+          <t>35,89; 41,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,45; 40,95</t>
+          <t>35,53; 40,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,03; 47,98</t>
+          <t>38,1; 47,61</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,03; 35,21</t>
+          <t>32,87; 35,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33,17; 35,21</t>
+          <t>33,1; 35,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,25; 46,53</t>
+          <t>36,19; 46,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,45; 36,71</t>
+          <t>34,4; 36,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,69; 35,99</t>
+          <t>33,72; 36,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,67; 42,59</t>
+          <t>38,43; 42,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,99; 35,61</t>
+          <t>33,96; 35,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,7; 35,27</t>
+          <t>33,74; 35,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,22; 43,22</t>
+          <t>38,22; 42,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
+          <t>Peso medio, en kilogramos, recogido por medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,73; 36,27</t>
+          <t>30,83; 36,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,02; 34,6</t>
+          <t>28,27; 34,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,23; 41,66</t>
+          <t>33,96; 41,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,5; 39,5</t>
+          <t>32,67; 39,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,39; 34,12</t>
+          <t>28,52; 34,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,67; 46,07</t>
+          <t>37,33; 46,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,43; 37,03</t>
+          <t>32,5; 36,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,13; 33,31</t>
+          <t>29,03; 33,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,28; 42,99</t>
+          <t>37,05; 43,14</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,12; 33,31</t>
+          <t>28,18; 33,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,2; 35,3</t>
+          <t>30,48; 35,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,36; 40,45</t>
+          <t>33,58; 40,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,79; 36,87</t>
+          <t>31,1; 37,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,13; 34,83</t>
+          <t>29,93; 35,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,88; 41,19</t>
+          <t>33,69; 41,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,3; 34,29</t>
+          <t>30,16; 34,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,76; 34,38</t>
+          <t>30,77; 34,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,53; 40,06</t>
+          <t>34,77; 39,94</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,32; 37,39</t>
+          <t>31,46; 37,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,66; 36,17</t>
+          <t>29,27; 35,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,12; 37,5</t>
+          <t>27,28; 37,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,18; 37,23</t>
+          <t>30,9; 37,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,18</t>
+          <t>33,45; 40,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,01; 46,72</t>
+          <t>33,77; 47,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,76; 36,75</t>
+          <t>32,09; 36,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,64; 37,46</t>
+          <t>32,66; 37,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,51; 41,91</t>
+          <t>32,62; 41,87</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,76; 35,69</t>
+          <t>31,66; 35,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,2; 37,06</t>
+          <t>33,16; 36,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,58; 52,37</t>
+          <t>34,58; 52,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,77; 36,77</t>
+          <t>32,66; 36,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,14; 37,66</t>
+          <t>33,27; 37,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,5; 45,15</t>
+          <t>35,19; 44,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,73; 35,59</t>
+          <t>32,84; 35,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,68; 36,7</t>
+          <t>33,72; 36,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,35; 47,97</t>
+          <t>36,43; 48,53</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,03; 37,67</t>
+          <t>33,21; 37,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 37,16</t>
+          <t>32,73; 36,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,7; 44,05</t>
+          <t>35,89; 44,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 39,75</t>
+          <t>34,14; 39,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 38,64</t>
+          <t>33,53; 38,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,06; 45,06</t>
+          <t>37,25; 45,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,44; 38,02</t>
+          <t>34,2; 37,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,82; 37,33</t>
+          <t>33,82; 37,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37,58; 43,87</t>
+          <t>37,67; 43,56</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,78; 44,11</t>
+          <t>33,68; 43,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,71; 42,07</t>
+          <t>33,97; 42,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,08; 46,36</t>
+          <t>33,48; 45,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,01; 42,41</t>
+          <t>35,13; 42,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,58; 41,44</t>
+          <t>34,37; 41,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,97; 52,86</t>
+          <t>39,18; 52,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,89; 41,68</t>
+          <t>35,27; 41,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,53; 40,52</t>
+          <t>35,5; 40,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,1; 47,61</t>
+          <t>37,71; 47,4</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,87; 35,15</t>
+          <t>32,97; 35,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33,1; 35,15</t>
+          <t>33,07; 35,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,19; 46,13</t>
+          <t>36,15; 45,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,4; 36,59</t>
+          <t>34,2; 36,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,72; 36,03</t>
+          <t>33,79; 36,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,43; 42,65</t>
+          <t>38,65; 42,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,96; 35,56</t>
+          <t>34,04; 35,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,74; 35,28</t>
+          <t>33,72; 35,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,22; 42,96</t>
+          <t>38,15; 43,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,91</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30,98</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41,88</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>33,38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>31,14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37,72</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35,91</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,98</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,42</t>
+          <t>38,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39,91</t>
+          <t>40,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,83; 36,79</t>
+          <t>32,54; 39,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,27; 34,99</t>
+          <t>28,33; 33,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,96; 41,06</t>
+          <t>37,93; 47,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,67; 39,63</t>
+          <t>30,75; 36,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,52; 34,18</t>
+          <t>28,15; 34,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,33; 46,05</t>
+          <t>34,74; 41,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,5; 36,95</t>
+          <t>32,35; 36,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 33,25</t>
+          <t>29,04; 33,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,05; 43,14</t>
+          <t>37,62; 43,6</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,68</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32,33</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38,11</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>30,63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>32,8</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36,91</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33,68</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>32,33</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,4</t>
+          <t>37,41</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,16</t>
+          <t>37,76</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,18; 33,57</t>
+          <t>30,89; 36,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,48; 35,51</t>
+          <t>29,95; 35,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,73</t>
+          <t>34,28; 41,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,1; 37,04</t>
+          <t>28,08; 33,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,93; 35,03</t>
+          <t>30,26; 35,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,69; 41,3</t>
+          <t>34,08; 41,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,16; 34,27</t>
+          <t>30,22; 34,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,77; 34,17</t>
+          <t>30,89; 34,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,77; 39,94</t>
+          <t>35,18; 40,51</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36,76</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41,36</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>34,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>32,51</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>34,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,76</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,75</t>
+          <t>32,31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36,82</t>
+          <t>37,75</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,46; 37,47</t>
+          <t>31,01; 37,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,27; 35,61</t>
+          <t>33,58; 40,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,28; 37,32</t>
+          <t>36,44; 48,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,9; 37,19</t>
+          <t>31,53; 37,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,45; 40,32</t>
+          <t>29,47; 35,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,77; 47,23</t>
+          <t>28,35; 37,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,09; 36,42</t>
+          <t>32,16; 36,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,66; 37,43</t>
+          <t>32,46; 37,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,62; 41,87</t>
+          <t>33,93; 42,71</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34,68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,33</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39,52</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>33,68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,85</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42,26</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,68</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,33</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,2</t>
+          <t>37,36</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40,84</t>
+          <t>38,5</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,66; 35,55</t>
+          <t>32,86; 36,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,16; 36,85</t>
+          <t>33,24; 37,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,58; 52,76</t>
+          <t>35,83; 44,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,66; 36,71</t>
+          <t>31,65; 35,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,27; 37,6</t>
+          <t>33,08; 36,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,19; 44,97</t>
+          <t>33,99; 41,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,84; 35,59</t>
+          <t>32,86; 35,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,72; 36,74</t>
+          <t>33,66; 36,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,43; 48,53</t>
+          <t>35,64; 41,6</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36,81</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36,09</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,88</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>35,32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>34,88</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>39,78</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36,81</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>36,09</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,94</t>
+          <t>39,54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40,48</t>
+          <t>40,95</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,21; 37,54</t>
+          <t>34,25; 39,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,73; 36,98</t>
+          <t>33,75; 39,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,89; 44,07</t>
+          <t>37,89; 46,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,14; 39,88</t>
+          <t>33,19; 37,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 38,88</t>
+          <t>32,61; 37,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,25; 45,25</t>
+          <t>35,06; 43,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,2; 37,86</t>
+          <t>34,46; 37,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,82; 37,18</t>
+          <t>33,79; 37,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37,67; 43,56</t>
+          <t>38,22; 44,38</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38,65</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37,89</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47,94</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>38,58</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>38,06</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38,13</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38,65</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>37,89</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,43</t>
+          <t>39,25</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42,39</t>
+          <t>44,08</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,68; 43,85</t>
+          <t>35,43; 42,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,97; 42,31</t>
+          <t>34,7; 41,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,48; 45,88</t>
+          <t>41,59; 54,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,13; 42,63</t>
+          <t>34,06; 43,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,37; 41,67</t>
+          <t>34,09; 42,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,18; 52,57</t>
+          <t>34,1; 46,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,27; 41,26</t>
+          <t>35,74; 41,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,5; 40,8</t>
+          <t>35,45; 40,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,71; 47,4</t>
+          <t>40,03; 49,58</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35,47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34,84</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41,32</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>34,07</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>34,18</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39,27</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35,47</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34,84</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,44</t>
+          <t>37,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>39,9</t>
+          <t>39,69</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,97; 35,17</t>
+          <t>34,45; 36,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33,07; 35,13</t>
+          <t>33,69; 35,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,15; 45,64</t>
+          <t>39,53; 43,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,2; 36,54</t>
+          <t>33,03; 35,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,79; 36,02</t>
+          <t>33,17; 35,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,65; 42,65</t>
+          <t>36,01; 39,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,04; 35,66</t>
+          <t>33,99; 35,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,72; 35,34</t>
+          <t>33,7; 35,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,15; 43,16</t>
+          <t>38,4; 41,25</t>
         </is>
       </c>
     </row>
